--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.817798130183142</v>
+        <v>0.6203921961547606</v>
       </c>
       <c r="D2" t="n">
-        <v>3.81257018277757</v>
+        <v>0.6195426547013551</v>
       </c>
       <c r="E2" t="n">
-        <v>21.68594132235394</v>
+        <v>3.523965464882516</v>
       </c>
       <c r="F2" t="n">
-        <v>21.4112033956308</v>
+        <v>3.479320551790005</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.75753849279314</v>
+        <v>9.060600005078886</v>
       </c>
       <c r="D3" t="n">
-        <v>55.09757222249652</v>
+        <v>8.953355486155685</v>
       </c>
       <c r="E3" t="n">
-        <v>21.68594132235394</v>
+        <v>3.523965464882516</v>
       </c>
       <c r="F3" t="n">
-        <v>21.4112033956308</v>
+        <v>3.479320551790005</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.14620794683906</v>
+        <v>3.273758791361348</v>
       </c>
       <c r="D4" t="n">
-        <v>19.9490329552734</v>
+        <v>3.241717855231928</v>
       </c>
       <c r="E4" t="n">
-        <v>21.68594132235394</v>
+        <v>3.523965464882516</v>
       </c>
       <c r="F4" t="n">
-        <v>21.4112033956308</v>
+        <v>3.479320551790005</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
